--- a/data/SESNSP, Trata de personas de 0 a 17 años en México, 2025.xlsx
+++ b/data/SESNSP, Trata de personas de 0 a 17 años en México, 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IPPI 11\Documents\GitHub\REDIM_1\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\GitHub\REDIM_1\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B36A141-3881-42EB-9342-91A3E5F0EF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2307562-68BC-4D33-8757-56DAFAF9A7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F370DC89-3D6A-45A3-B06C-224CF83F682F}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{F370DC89-3D6A-45A3-B06C-224CF83F682F}"/>
   </bookViews>
   <sheets>
     <sheet name="estados" sheetId="2" r:id="rId1"/>
@@ -24,8 +24,16 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -365,7 +373,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -378,13 +386,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -426,28 +427,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -804,14 +806,14 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:H33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="26.75" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="24.875" customWidth="1"/>
+    <col min="5" max="5" width="24.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -837,7 +839,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -863,7 +865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -889,7 +891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -915,7 +917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -941,7 +943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -967,7 +969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -993,7 +995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1019,7 +1021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1045,7 +1047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1071,7 +1073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1097,7 +1099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1123,7 +1125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1149,7 +1151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1175,7 +1177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1201,7 +1203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1227,7 +1229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1253,7 +1255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1279,7 +1281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1305,7 +1307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1331,7 +1333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1357,7 +1359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1383,7 +1385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1409,7 +1411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1435,7 +1437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1461,7 +1463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1487,7 +1489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1513,7 +1515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1539,7 +1541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1565,7 +1567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1591,7 +1593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1617,7 +1619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1643,7 +1645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1680,733 +1682,769 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B5AC18-3362-4E46-983D-66A308125C57}">
   <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.375" customWidth="1"/>
-    <col min="2" max="5" width="15.25" customWidth="1"/>
+    <col min="1" max="1" width="37.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" customWidth="1"/>
+    <col min="6" max="6" width="57.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
+    <row r="1" spans="1:6" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="7">
-        <v>0</v>
-      </c>
-      <c r="C2" s="7">
-        <v>1</v>
-      </c>
-      <c r="D2" s="7">
-        <v>1</v>
-      </c>
-      <c r="E2" s="8">
+      <c r="B2" s="5">
         <f>VLOOKUP(A2,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="F2" s="3" t="str">
-        <f>"INSERT INTO sesnsp (state_id, woman, man) VALUES (" &amp; E2 &amp; ", " &amp; C2 &amp; ", " &amp; B2 &amp; ");"</f>
-        <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (1, 1, 0);</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15">
-      <c r="A3" s="9" t="s">
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <f>SUM(C2:D2)</f>
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="str">
+        <f>"INSERT INTO sesnsp (state_id, woman, man) VALUES (" &amp; B2 &amp; ", " &amp; D2 &amp; ", " &amp; C2 &amp; ");"</f>
+        <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (1, 0, 1);</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="7">
-        <v>4</v>
-      </c>
-      <c r="C3" s="7">
-        <v>12</v>
-      </c>
-      <c r="D3" s="7">
-        <v>16</v>
-      </c>
-      <c r="E3" s="8">
+      <c r="B3" s="5">
         <f>VLOOKUP(A3,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="str">
-        <f t="shared" ref="F3:F33" si="0">"INSERT INTO sesnsp (state_id, woman, man) VALUES (" &amp; E3 &amp; ", " &amp; C3 &amp; ", " &amp; B3 &amp; ");"</f>
+      <c r="C3" s="3">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3">
+        <f t="shared" ref="E3:E33" si="0">SUM(C3:D3)</f>
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="str">
+        <f t="shared" ref="F3:F33" si="1">"INSERT INTO sesnsp (state_id, woman, man) VALUES (" &amp; B3 &amp; ", " &amp; C3 &amp; ", " &amp; D3 &amp; ");"</f>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (2, 12, 4);</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7">
-        <v>3</v>
-      </c>
-      <c r="C4" s="7">
-        <v>4</v>
-      </c>
-      <c r="D4" s="7">
-        <v>7</v>
-      </c>
-      <c r="E4" s="8">
+      <c r="B4" s="5">
         <f>VLOOKUP(A4,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="C4" s="3">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="F4" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (3, 4, 3);</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="7">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7">
-        <v>1</v>
-      </c>
-      <c r="D5" s="7">
-        <v>1</v>
-      </c>
-      <c r="E5" s="8">
+      <c r="B5" s="5">
         <f>VLOOKUP(A5,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="F5" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (4, 1, 0);</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7">
-        <v>2</v>
-      </c>
-      <c r="C6" s="7">
-        <v>4</v>
-      </c>
-      <c r="D6" s="7">
-        <v>6</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="B6" s="5">
         <f>VLOOKUP(A6,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>5</v>
       </c>
-      <c r="F6" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="C6" s="3">
+        <v>4</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F6" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (5, 4, 2);</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7">
-        <v>13</v>
-      </c>
-      <c r="C7" s="7">
-        <v>21</v>
-      </c>
-      <c r="D7" s="7">
-        <v>34</v>
-      </c>
-      <c r="E7" s="8">
+      <c r="B7" s="5">
         <f>VLOOKUP(A7,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="F7" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="C7" s="3">
+        <v>21</v>
+      </c>
+      <c r="D7" s="3">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="F7" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (6, 21, 13);</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="7">
-        <v>6</v>
-      </c>
-      <c r="C8" s="7">
-        <v>16</v>
-      </c>
-      <c r="D8" s="7">
-        <v>22</v>
-      </c>
-      <c r="E8" s="8">
+      <c r="B8" s="5">
         <f>VLOOKUP(A8,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="F8" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="C8" s="3">
+        <v>16</v>
+      </c>
+      <c r="D8" s="3">
+        <v>6</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="F8" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (7, 16, 6);</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="7">
-        <v>1</v>
-      </c>
-      <c r="C9" s="7">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7">
-        <v>3</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="B9" s="5">
         <f>VLOOKUP(A9,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>8</v>
       </c>
-      <c r="F9" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F9" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (8, 2, 1);</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="7">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8">
+      <c r="B10" s="5">
         <f>VLOOKUP(A10,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>9</v>
       </c>
-      <c r="F10" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (9, 0, 0);</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="7">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7">
-        <v>0</v>
-      </c>
-      <c r="E11" s="8">
+      <c r="B11" s="5">
         <f>VLOOKUP(A11,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>10</v>
       </c>
-      <c r="F11" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (10, 0, 0);</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="7">
-        <v>2</v>
-      </c>
-      <c r="C12" s="7">
-        <v>3</v>
-      </c>
-      <c r="D12" s="7">
-        <v>5</v>
-      </c>
-      <c r="E12" s="8">
+      <c r="B12" s="5">
         <f>VLOOKUP(A12,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>11</v>
       </c>
-      <c r="F12" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C12" s="3">
+        <v>3</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F12" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (11, 3, 2);</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="7">
-        <v>3</v>
-      </c>
-      <c r="C13" s="7">
-        <v>12</v>
-      </c>
-      <c r="D13" s="7">
-        <v>15</v>
-      </c>
-      <c r="E13" s="8">
+      <c r="B13" s="5">
         <f>VLOOKUP(A13,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>12</v>
       </c>
-      <c r="F13" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C13" s="3">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F13" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (12, 12, 3);</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="7">
-        <v>0</v>
-      </c>
-      <c r="C14" s="7">
-        <v>3</v>
-      </c>
-      <c r="D14" s="7">
-        <v>3</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="B14" s="5">
         <f>VLOOKUP(A14,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>13</v>
       </c>
-      <c r="F14" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C14" s="3">
+        <v>3</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F14" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (13, 3, 0);</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="7">
-        <v>5</v>
-      </c>
-      <c r="C15" s="7">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7">
-        <v>5</v>
-      </c>
-      <c r="E15" s="8">
+      <c r="B15" s="5">
         <f>VLOOKUP(A15,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>14</v>
       </c>
-      <c r="F15" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F15" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (14, 0, 5);</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="7">
-        <v>11</v>
-      </c>
-      <c r="C16" s="7">
-        <v>31</v>
-      </c>
-      <c r="D16" s="7">
-        <v>42</v>
-      </c>
-      <c r="E16" s="8">
+      <c r="B16" s="5">
         <f>VLOOKUP(A16,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>15</v>
       </c>
-      <c r="F16" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C16" s="3">
+        <v>31</v>
+      </c>
+      <c r="D16" s="3">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="F16" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (15, 31, 11);</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="7">
-        <v>0</v>
-      </c>
-      <c r="C17" s="7">
-        <v>1</v>
-      </c>
-      <c r="D17" s="7">
-        <v>1</v>
-      </c>
-      <c r="E17" s="8">
+      <c r="B17" s="5">
         <f>VLOOKUP(A17,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>16</v>
       </c>
-      <c r="F17" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F17" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (16, 1, 0);</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="7">
-        <v>0</v>
-      </c>
-      <c r="C18" s="7">
-        <v>3</v>
-      </c>
-      <c r="D18" s="7">
-        <v>3</v>
-      </c>
-      <c r="E18" s="8">
+      <c r="B18" s="5">
         <f>VLOOKUP(A18,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>17</v>
       </c>
-      <c r="F18" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C18" s="3">
+        <v>3</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F18" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (17, 3, 0);</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="7">
-        <v>0</v>
-      </c>
-      <c r="C19" s="7">
-        <v>1</v>
-      </c>
-      <c r="D19" s="7">
-        <v>1</v>
-      </c>
-      <c r="E19" s="8">
+      <c r="B19" s="5">
         <f>VLOOKUP(A19,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>18</v>
       </c>
-      <c r="F19" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C19" s="3">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F19" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (18, 1, 0);</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="7">
-        <v>0</v>
-      </c>
-      <c r="C20" s="7">
-        <v>7</v>
-      </c>
-      <c r="D20" s="7">
-        <v>7</v>
-      </c>
-      <c r="E20" s="8">
+      <c r="B20" s="5">
         <f>VLOOKUP(A20,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>19</v>
       </c>
-      <c r="F20" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C20" s="3">
+        <v>7</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="F20" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (19, 7, 0);</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="7">
-        <v>3</v>
-      </c>
-      <c r="C21" s="7">
-        <v>6</v>
-      </c>
-      <c r="D21" s="7">
-        <v>9</v>
-      </c>
-      <c r="E21" s="8">
+      <c r="B21" s="5">
         <f>VLOOKUP(A21,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>20</v>
       </c>
-      <c r="F21" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C21" s="3">
+        <v>6</v>
+      </c>
+      <c r="D21" s="3">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="F21" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (20, 6, 3);</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="7">
-        <v>5</v>
-      </c>
-      <c r="C22" s="7">
-        <v>5</v>
-      </c>
-      <c r="D22" s="7">
-        <v>10</v>
-      </c>
-      <c r="E22" s="8">
+      <c r="B22" s="5">
         <f>VLOOKUP(A22,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>21</v>
       </c>
-      <c r="F22" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C22" s="3">
+        <v>5</v>
+      </c>
+      <c r="D22" s="3">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F22" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (21, 5, 5);</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="7">
-        <v>0</v>
-      </c>
-      <c r="C23" s="7">
-        <v>0</v>
-      </c>
-      <c r="D23" s="7">
-        <v>0</v>
-      </c>
-      <c r="E23" s="8">
+      <c r="B23" s="5">
         <f>VLOOKUP(A23,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>22</v>
       </c>
-      <c r="F23" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C23" s="3">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (22, 0, 0);</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="7">
-        <v>17</v>
-      </c>
-      <c r="C24" s="7">
-        <v>53</v>
-      </c>
-      <c r="D24" s="7">
-        <v>70</v>
-      </c>
-      <c r="E24" s="8">
+      <c r="B24" s="5">
         <f>VLOOKUP(A24,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>23</v>
       </c>
-      <c r="F24" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C24" s="3">
+        <v>53</v>
+      </c>
+      <c r="D24" s="3">
+        <v>17</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="F24" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (23, 53, 17);</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="6" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="7">
-        <v>0</v>
-      </c>
-      <c r="C25" s="7">
-        <v>11</v>
-      </c>
-      <c r="D25" s="7">
-        <v>11</v>
-      </c>
-      <c r="E25" s="8">
+      <c r="B25" s="5">
         <f>VLOOKUP(A25,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>24</v>
       </c>
-      <c r="F25" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C25" s="3">
+        <v>11</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F25" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (24, 11, 0);</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="6" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="7">
-        <v>0</v>
-      </c>
-      <c r="C26" s="7">
-        <v>0</v>
-      </c>
-      <c r="D26" s="7">
-        <v>0</v>
-      </c>
-      <c r="E26" s="8">
+      <c r="B26" s="5">
         <f>VLOOKUP(A26,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>25</v>
       </c>
-      <c r="F26" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C26" s="3">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (25, 0, 0);</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="6" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="7">
-        <v>1</v>
-      </c>
-      <c r="C27" s="7">
-        <v>2</v>
-      </c>
-      <c r="D27" s="7">
-        <v>3</v>
-      </c>
-      <c r="E27" s="8">
+      <c r="B27" s="5">
         <f>VLOOKUP(A27,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>26</v>
       </c>
-      <c r="F27" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C27" s="3">
+        <v>2</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F27" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (26, 2, 1);</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="6" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="7">
-        <v>0</v>
-      </c>
-      <c r="C28" s="7">
-        <v>5</v>
-      </c>
-      <c r="D28" s="7">
-        <v>5</v>
-      </c>
-      <c r="E28" s="8">
+      <c r="B28" s="5">
         <f>VLOOKUP(A28,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>27</v>
       </c>
-      <c r="F28" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C28" s="3">
+        <v>5</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F28" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (27, 5, 0);</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="7">
-        <v>0</v>
-      </c>
-      <c r="C29" s="7">
-        <v>3</v>
-      </c>
-      <c r="D29" s="7">
-        <v>3</v>
-      </c>
-      <c r="E29" s="8">
+      <c r="B29" s="5">
         <f>VLOOKUP(A29,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>28</v>
       </c>
-      <c r="F29" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C29" s="3">
+        <v>3</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F29" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (28, 3, 0);</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="6" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="7">
-        <v>0</v>
-      </c>
-      <c r="C30" s="7">
-        <v>0</v>
-      </c>
-      <c r="D30" s="7">
-        <v>0</v>
-      </c>
-      <c r="E30" s="8">
+      <c r="B30" s="5">
         <f>VLOOKUP(A30,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>29</v>
       </c>
-      <c r="F30" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C30" s="3">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (29, 0, 0);</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B31" s="7">
-        <v>2</v>
-      </c>
-      <c r="C31" s="7">
-        <v>2</v>
-      </c>
-      <c r="D31" s="7">
-        <v>4</v>
-      </c>
-      <c r="E31" s="8">
+      <c r="B31" s="5">
         <f>VLOOKUP(A31,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>30</v>
       </c>
-      <c r="F31" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C31" s="3">
+        <v>2</v>
+      </c>
+      <c r="D31" s="3">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F31" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (30, 2, 2);</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="7">
-        <v>0</v>
-      </c>
-      <c r="C32" s="7">
-        <v>0</v>
-      </c>
-      <c r="D32" s="7">
-        <v>0</v>
-      </c>
-      <c r="E32" s="8">
+      <c r="B32" s="5">
         <f>VLOOKUP(A32,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>31</v>
       </c>
-      <c r="F32" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C32" s="3">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (31, 0, 0);</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="7">
-        <v>2</v>
-      </c>
-      <c r="C33" s="7">
-        <v>12</v>
-      </c>
-      <c r="D33" s="7">
-        <v>14</v>
-      </c>
-      <c r="E33" s="8">
+      <c r="B33" s="5">
         <f>VLOOKUP(A33,Tabla3[[name]:[ID_2]],2,FALSE)</f>
         <v>32</v>
       </c>
-      <c r="F33" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="C33" s="3">
+        <v>12</v>
+      </c>
+      <c r="D33" s="3">
+        <v>2</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="F33" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO sesnsp (state_id, woman, man) VALUES (32, 12, 2);</v>
       </c>
     </row>

--- a/data/SESNSP, Trata de personas de 0 a 17 años en México, 2025.xlsx
+++ b/data/SESNSP, Trata de personas de 0 a 17 años en México, 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\GitHub\REDIM_1\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2307562-68BC-4D33-8757-56DAFAF9A7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069AD062-F21D-4413-B86C-1B858C7610CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{F370DC89-3D6A-45A3-B06C-224CF83F682F}"/>
   </bookViews>
@@ -1736,7 +1736,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="5">
@@ -1759,7 +1759,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="5">
@@ -1782,7 +1782,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="5">
@@ -1805,7 +1805,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="5">
@@ -1828,7 +1828,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="5">
@@ -1851,7 +1851,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="5">
@@ -1874,7 +1874,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B9" s="5">
@@ -1897,7 +1897,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="5">
@@ -1920,7 +1920,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="5">
@@ -2380,7 +2380,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="4" t="s">
         <v>100</v>
       </c>
       <c r="B31" s="5">
